--- a/AI Audit Log_MacTuHau.xlsx
+++ b/AI Audit Log_MacTuHau.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\ai-audit-log-mactuhau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5392AB06-AB39-4A73-9772-F26E38E421B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B52E7D-D0BC-4F8C-8FFF-0F6D82DD5FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="2" r:id="rId1"/>
     <sheet name="Week 2" sheetId="1" r:id="rId2"/>
-    <sheet name="Assignment 3" sheetId="4" r:id="rId3"/>
+    <sheet name="Week 3" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -174,6 +174,78 @@
   <si>
     <t>Phản hồi: AI phân biệt rõ sự khác nhau giữa Local Database và Cloud Database. Đồng thời gợi ý dùng gói Azure for Students để tạo server chung hoặc dùng phần mềm Ngrok để mở port máy cá nhân.
 Kiểm chứng &amp; Quyết định: AI không biết rằng tài khoản Azure Student của tôi đang bị lỗi xác thực thẻ (Unable to complete verification). Hơn nữa, việc dùng Ngrok đòi hỏi tôi phải bật máy tính 24/24. Dựa trên tình hình thực tế, tôi đã tự đưa ra giải pháp mới: nhờ một bạn trong nhóm chưa từng dùng Azure dùng email của bạn đó tạo Server, sau đó tôi sẽ đảm nhận việc deploy Database từ máy Local của tôi lên Server đó. Quyết định này giúp nhóm có môi trường làm việc chung 24/7 cực kỳ ổn định mà không tốn chi phí hay phải treo máy liên tục.</t>
+  </si>
+  <si>
+    <t>"Implement the Login page from Figma node 6-2, following 20 architecture rules (feature-based, Zustand, React Query, Zod…)"</t>
+  </si>
+  <si>
+    <t>AI split features/auth/ into api/, services/, hooks/, stores/, validations/, components/, pages/; reusable UI into shared/components/ (InputField, Checkbox, Divider). Decision: Accepted the structure; enforced all API calls through authApi → authService → React Query hooks — never directly in UI. Build passed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+Pattern Recognition / Evaluation</t>
+  </si>
+  <si>
+    <t>"Migrate auth from Redux to Zustand; update useAuth, axiosInstance, ProfileMenu"</t>
+  </si>
+  <si>
+    <t>AI created shared/stores/authStore.ts (global session) and loginStore.ts (UI: rememberMe, showPassword). Decision: Separated global vs feature stores (rule 13); migrated auth only, did not remove Redux project-wide to avoid breaking other modules.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+Problem Solving</t>
+  </si>
+  <si>
+    <t>"Implement Register from Figma node 6-107, reusing the Login pattern"</t>
+  </si>
+  <si>
+    <t>AI refactored AuthBrandPanel with titleLines prop, added registerSchema, useRegister, registerStore. Decision: Reused login.css for split layout; used Zod .refine() for confirmPassword matching.</t>
+  </si>
+  <si>
+    <t>"Implement the 5-screen Forgot Password flow (Figma 6-216 → 6-532)"</t>
+  </si>
+  <si>
+    <t>AI designed multi-step flow: forgotPasswordStore (method, contact, cooldown, isOtpVerified) + forgotPasswordSuccessStore. Decision: Route chain /forgot-password → /verify → /otp → /reset → /success; guard redirects when state is missing.</t>
+  </si>
+  <si>
+    <t>"Create reusable components for OTP input and method selection cards"</t>
+  </si>
+  <si>
+    <t>AI placed SelectionCard, OtpInput, SuccessIcon, SuccessState in shared/components/. Decision: Generic UI in shared; auth-specific copy/layout in feature. OtpInput supports paste, auto-focus, and keyboard navigation.</t>
+  </si>
+  <si>
+    <t>"Figma MCP quota exhausted — implement OTP / Reset / Success screens"</t>
+  </si>
+  <si>
+    <t>AI could not read nodes 6-382, 6-459, 6-532; inferred layout from prior screens (32px title, primary button + arrow, support footer). Decision: Implemented using existing patterns; pixel-perfect review needed when MCP quota is available. npm run build passed.</t>
+  </si>
+  <si>
+    <t>"Merge main into hau — ProfileMenu.jsx conflict (3 conflicts)"</t>
+  </si>
+  <si>
+    <t>main used Redux dispatch(logout()); hau used Zustand clearAuthSession() + navigate('/login'). Decision: Kept the hau version since auth was already migrated; rejected Redux revert. Merge completed successfully.</t>
+  </si>
+  <si>
+    <t>Evaluation</t>
+  </si>
+  <si>
+    <t>"Handle backend API not yet available"</t>
+  </si>
+  <si>
+    <t>AI added demo fallback: Promise.race with 3s timeout → mock response for login/register/forgot-password. Decision: Accepted for dev/demo; replace with real error handling when BE is deployed.</t>
+  </si>
+  <si>
+    <t>"Validation schemas for each forgot-password step"</t>
+  </si>
+  <si>
+    <t>AI created separate schemas: email/phone verify, 6-digit OTP, reset password + confirm. Decision: One schema per step instead of a monolithic schema; phone regex (0|+84)[0-9]{9,10} for Vietnam.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+"Test full flow on dev server"</t>
+  </si>
+  <si>
+    <t>Multiple stale instances occupied ports 5173–5179 → new server on 5180. Decision: Used temporarily; kill old processes before demo. Flow: / → /login → forgot-password → success → /login.</t>
   </si>
 </sst>
 </file>
@@ -924,9 +996,171 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" customWidth="1"/>
+    <col min="4" max="4" width="76.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="5" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+      <c r="A1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="4"/>
+    </row>
+    <row r="2" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/AI Audit Log_MacTuHau.xlsx
+++ b/AI Audit Log_MacTuHau.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\ai-audit-log-mactuhau\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{94B52E7D-D0BC-4F8C-8FFF-0F6D82DD5FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6721879E-BE65-4152-BD28-48801D6BA9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
   </bookViews>
   <sheets>
     <sheet name="Week 1" sheetId="2" r:id="rId1"/>
     <sheet name="Week 2" sheetId="1" r:id="rId2"/>
     <sheet name="Week 3" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="86">
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -246,13 +247,95 @@
   </si>
   <si>
     <t>Multiple stale instances occupied ports 5173–5179 → new server on 5180. Decision: Used temporarily; kill old processes before demo. Flow: / → /login → forgot-password → success → /login.</t>
+  </si>
+  <si>
+    <t>Viết test plan toàn diện cho phân hệ Đăng nhập và Thanh toán của hệ thống SEHUB, bao gồm cả ma trận kiểm thử (Traceability Matrix).</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI liệt kê đầy đủ các mục tiêu theo chuẩn IEEE 829, tuy nhiên phần phân rã tính năng bị dàn trải, các kịch bản kiểm thử biên (Boundary Value) và phân vùng tương đương (Equivalence Partitioning) cho phần nhập Token/Số tiền thanh toán bị sơ sài.
+- Quyết định (Human Delta): Tôi chấp nhận cấu trúc khung của AI nhưng tự tay phân rã lại ma trận. Tôi bổ sung thêm các case kiểm thử kiểm tra số dư âm, giá trị vượt ngưỡng int.MaxValue, và kịch bản mạng đứt quãng khi cổng thanh toán đang xử lý (Callback) để đảm bảo không bị lỗi logic nghiêm trọng.</t>
+  </si>
+  <si>
+    <t>Tạo 20 Test Cases bằng kỹ thuật Bảng quyết định (Decision Table) cho tính năng phân quyền Admin/Giảng viên/Sinh viên duyệt đề thi.</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI nhận diện tốt mẫu (Pattern) của bảng quyết định với các cột Điều kiện (Conditions) và Hành động (Actions), sinh ra file Excel giả lập.
+- Kiểm chứng &amp; Quyết định: Tôi phát hiện AI gom chung quyền "Giảng viên" và "Admin" ở một số case chỉnh sửa cấu hình hệ thống. Dựa trên Business Rule thực tế của dự án, tôi đã loại bỏ 4 case bị trùng lặp logic và siết chặt lại quyền của Giảng viên (chỉ được sửa đề thi do mình tạo ra), tránh lỗ hổng leo thang đặc quyền (Privilege Escalation).</t>
+  </si>
+  <si>
+    <t>Viết mã script Automation Test bằng Selenium (C#) để test luồng Đăng ký tài khoản có kiểm tra OTP.</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI sinh code sử dụng hàm Thread.Sleep(5000) để chờ hệ thống gửi và nhận OTP, sau đó điền cứng một mã OTP giả lập.
+- Kiểm chứng &amp; Quyết định: Cách làm của AI là một "Bad Practice" vì Thread.Sleep gây lãng phí thời gian chạy test và dễ làm hỏng build (Flaky Test) nếu mạng chậm. Tôi đã xóa bỏ toàn bộ các dòng Thread.Sleep và cấu hình lại bằng WebDriverWait kết hợp với ExpectedConditions (Explicit Wait). Đồng thời, tôi viết thêm hàm mock API nhận OTP từ cơ sở dữ liệu để luồng test chạy tự động 100% với tốc độ tối ưu.</t>
+  </si>
+  <si>
+    <t>Thiết kế bộ dữ liệu kiểm thử (Test Data Injection) dạng CSV để thực hiện Data-Driven Testing cho tính năng tạo câu hỏi trắc nghiệm.</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI tạo file CSV chứa các ký tự thông thường và một vài chuỗi dài.
+- Quyết định (Human Delta): Bộ dữ liệu của AI quá "sạch", chưa đủ khả năng làm sập hệ thống. Tôi áp dụng kỹ năng trừu tượng hóa các rủi ro bảo mật để nâng cấp file CSV: thêm vào các chuỗi có chứa ký tự đặc biệt (!@#$%^&amp;*), các đoạn mã độc SQL Injection (' OR 1=1 --'), và script XSS (&lt;script&gt;alert(1)&lt;/script&gt;) để kiểm tra khả năng Validation/Sanitize dữ liệu đầu vào của Backend.</t>
+  </si>
+  <si>
+    <t>Chạy thử script Automation Test trên môi trường CI/CD (GitHub Actions) nhưng bị báo lỗi 'Chrome failed to start: crashed' trên Runner Linux.</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI gợi ý cập nhật phiên bản Chrome trên máy cá nhân hoặc kiểm tra lại file cấu hình dự án.
+- Kiểm chứng &amp; Quyết định: Lời khuyên của AI không đúng trọng tâm vì lỗi xảy ra trên môi trường Docker Linux của GitHub Actions chứ không phải máy local. Qua phân tích log, tôi nhận ra Chrome trên Linux cần chạy ở chế độ không giao diện. Tôi đã chủ động thêm các đối số --headless, --no-sandbox, và --disable-dev-shm-usage vào phần khởi tạo ChromeOptions trong code. Kết quả: Pipeline build thành công, test suite chạy mượt mà.</t>
+  </si>
+  <si>
+    <t>Decomposition / Evaluation</t>
+  </si>
+  <si>
+    <t>Sử dụng công cụ JMeter để cấu hình kịch bản Performance Test (Kiểm thử hiệu năng) cho API lấy danh sách phòng chat với 500 users truy cập cùng lúc (Concurrent Users).</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI hướng dẫn tạo một Thread Group cơ bản với Ramp-up period là 1 giây để đổ dồn 500 requests vào hệ thống ngay lập tức.
+- Quyết định (Human Delta): Cách này sẽ tạo ra đỉnh tải ảo không thực tế (Spike Test) thay vì đo hiệu năng chịu tải bền vững (Load Test). Tôi đã điều chỉnh cấu hình Ramp-up thành 60 giây để lượng user tăng dần đều, đồng thời thêm Constant Timer (nghỉ 1-2s giữa các request) để giả lập hành vi "suy nghĩ" thực tế của người dùng, giúp biểu đồ kết quả Throughput và Response Time chính xác hơn.</t>
+  </si>
+  <si>
+    <t>Dựa vào mã nguồn backend của controller ExamController.cs, hãy chỉ ra các vùng code chưa được bao phủ bởi Unit Test (Code Coverage).</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI quét qua file code và liệt kê các hàm chưa có file test tương ứng.
+- Kiểm chứng &amp; Quyết định: AI chỉ nhận diện theo bề nổi tên hàm. Tôi đã dùng công cụ Coverlet trong .NET để kiểm tra độ bao phủ thực tế và phát hiện AI bỏ sót các nhánh điều kiện ẩn (Branch Coverage) nằm trong các khối try-catch và các câu lệnh if-else lồng nhau. Tôi đã tự viết bổ sung 6 Unit Test tập trung chính xác vào các nhánh ngoại lệ (Exception Handling) này để nâng Coverage từ 65% lên 92%.</t>
+  </si>
+  <si>
+    <t>Problem Solving</t>
+  </si>
+  <si>
+    <t>Khi thực hiện API Testing bằng Postman, làm sao để tự động trích xuất accessToken từ phản hồi của API Login để dùng cho các API sau mà không phải copy-paste thủ công?</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI viết một đoạn script đặt trong tab Tests bằng cú pháp cũ của Postman (tests["Status code is 200"] = responseCode.code === 200;).
+- Kiểm chứng &amp; Quyết định: Cú pháp của AI đã lỗi thời (Deprecated). Tôi đã tự cập nhật lại đoạn script theo chuẩn mới pm.test() và sử dụng pm.environment.set("token", pm.response.json().data.accessToken);. Giải pháp này giúp tự động hóa hoàn toàn chuỗi kiểm thử các API phía sau mà không bị cảnh báo lỗi cú pháp từ Postman.</t>
+  </si>
+  <si>
+    <t>Verification / Evaluation</t>
+  </si>
+  <si>
+    <t>Đánh giá kết quả báo cáo Bug Report: AI tìm thấy 3 lỗi giao diện (UI) lệch 2px trên thiết bị di động và phân loại chúng là mức độ Nghiêm trọng (High Severity).</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI khẳng định các lỗi này làm giảm trải nghiệm người dùng nghiêm trọng và cần block việc release.
+- Quyết định (Human Delta): Tôi bác bỏ đánh giá của AI. Lỗi lệch 2px chỉ là lỗi thẩm mỹ (Cosmetic Bug), không gây mất chức năng hay treo ứng dụng. Dựa trên quy trình quản lý chất lượng thực tế, tôi hạ mức độ xuống thành Thấp (Low Severity / Minor Priority) để nhường tài nguyên cho đội Dev tập trung fix các lỗi logic core liên quan đến mất dữ liệu, tránh làm chậm tiến độ release của dự án.</t>
+  </si>
+  <si>
+    <t>Abstraction / Algorithmic Thinking</t>
+  </si>
+  <si>
+    <t>Thiết kế kịch bản kiểm thử bảo mật (Security Testing) cho tính năng upload tài liệu bài tập của sinh viên (.pdf, .docx).</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI gợi ý kiểm tra xem hệ thống có chặn các file đuôi .exe hay .bat hay không.
+- Quyết định (Human Delta): Ý tưởng của AI quá cơ bản và dễ dàng bị bypass. Tôi áp dụng tư duy "Hacker" để mở rộng kịch bản: Thay vì chỉ kiểm tra đuôi file (Extension), tôi thiết kế case kiểm thử đổi đuôi file từ malware.exe thành malware.pdf nhưng bản chất bên trong vẫn là mã độc (kiểm tra MIME type/Magic Number). Tôi cũng thêm kịch bản nén file bom dung lượng (Zip Bomb) để test xem hệ thống có bị nghẽn RAM khi giải nén hay không, giúp tối ưu hóa tầng bảo mật cho ứng dụng.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -279,8 +362,25 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -311,8 +411,14 @@
         <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E78"/>
+        <bgColor rgb="FF1F4E78"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -350,11 +456,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD3D3D3"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD3D3D3"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD3D3D3"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD3D3D3"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -383,6 +504,18 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -719,15 +852,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" customWidth="1"/>
-    <col min="2" max="2" width="31.85546875" customWidth="1"/>
-    <col min="3" max="3" width="33.140625" customWidth="1"/>
-    <col min="4" max="4" width="59.140625" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" customWidth="1"/>
+    <col min="2" max="2" width="31.88671875" customWidth="1"/>
+    <col min="3" max="3" width="33.109375" customWidth="1"/>
+    <col min="4" max="4" width="59.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="5" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="10" t="s">
         <v>3</v>
       </c>
@@ -742,7 +875,7 @@
       </c>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:5" ht="206.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="206.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -756,7 +889,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="267" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="267" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="8">
         <v>2</v>
       </c>
@@ -770,49 +903,49 @@
         <v>38</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -826,15 +959,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" customWidth="1"/>
-    <col min="4" max="4" width="76.28515625" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" customWidth="1"/>
+    <col min="4" max="4" width="76.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="5" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
@@ -849,7 +982,7 @@
       </c>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -863,7 +996,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -877,7 +1010,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -891,7 +1024,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -905,7 +1038,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -919,7 +1052,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="72" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -933,7 +1066,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -947,7 +1080,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -961,7 +1094,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="120" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -975,7 +1108,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="105" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -997,15 +1130,15 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="26.85546875" customWidth="1"/>
-    <col min="3" max="3" width="24.28515625" customWidth="1"/>
-    <col min="4" max="4" width="76.28515625" customWidth="1"/>
+    <col min="2" max="2" width="26.88671875" customWidth="1"/>
+    <col min="3" max="3" width="24.33203125" customWidth="1"/>
+    <col min="4" max="4" width="76.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" s="5" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
@@ -1020,7 +1153,7 @@
       </c>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:5" ht="90" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1034,7 +1167,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1048,7 +1181,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1062,7 +1195,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1076,7 +1209,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1090,7 +1223,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1104,7 +1237,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1118,7 +1251,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1132,7 +1265,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1146,7 +1279,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1158,6 +1291,175 @@
       </c>
       <c r="D11" s="2" t="s">
         <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540CDA82-72CC-4977-B394-F64FA908FB7E}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="48.109375" customWidth="1"/>
+    <col min="3" max="3" width="39" customWidth="1"/>
+    <col min="4" max="4" width="85.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="167.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="12">
+        <v>1</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="14" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="12">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="14" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="12">
+        <v>3</v>
+      </c>
+      <c r="B4" s="13" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="14" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="12">
+        <v>4</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="14" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="12">
+        <v>5</v>
+      </c>
+      <c r="B6" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="14" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="12">
+        <v>6</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="14" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="12">
+        <v>7</v>
+      </c>
+      <c r="B8" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="12">
+        <v>8</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="12">
+        <v>9</v>
+      </c>
+      <c r="B10" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="12">
+        <v>10</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/AI Audit Log_MacTuHau.xlsx
+++ b/AI Audit Log_MacTuHau.xlsx
@@ -2,38 +2,27 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\GitHub\ai-audit-log-mactuhau\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6721879E-BE65-4152-BD28-48801D6BA9EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF7C4DB6-32ED-4160-8C38-7833E2EA5161}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{84C35D15-8A6C-4EDA-8B49-2CCD89DED56E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Week 1" sheetId="2" r:id="rId1"/>
-    <sheet name="Week 2" sheetId="1" r:id="rId2"/>
-    <sheet name="Week 3" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="5" r:id="rId4"/>
+    <sheet name="Week 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Week 2" sheetId="2" r:id="rId2"/>
+    <sheet name="Week 3" sheetId="3" r:id="rId3"/>
+    <sheet name="Week 4" sheetId="4" r:id="rId4"/>
+    <sheet name="Week 5" sheetId="5" r:id="rId5"/>
+    <sheet name="Week 6" sheetId="6" r:id="rId6"/>
+    <sheet name="Week 7" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -42,7 +31,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="152">
+  <si>
+    <t>STT</t>
+  </si>
   <si>
     <t>Giai đoạn/Thành phần DTC</t>
   </si>
@@ -53,7 +45,28 @@
     <t>Phản hồi của AI &amp; Quyết định của người học (Reflection)</t>
   </si>
   <si>
-    <t>STT</t>
+    <t>Problem-Solving
+(Environment Setup / Tooling)</t>
+  </si>
+  <si>
+    <t>Prompt: "fĩx XHR failed"
+(Kèm ảnh chụp màn hình báo lỗi XHR failed trên tab Extension của Azure Data Studio).</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phân tích nguyên nhân lỗi mạng và đề xuất 4 phương án: (1) Tắt Strict SSL, (2) Cấu hình Proxy, (3) Tắt IPv6/Đổi DNS, (4) Tải thủ công file .vsix để cài offline.
+Kiểm chứng &amp; Quyết định: Tôi nhận định việc can thiệp vào hệ thống mạng (tắt IPv6 hay đổi DNS) có thể gây lỗi mạng cho các phần mềm khác trên máy. Do đó, tôi chủ động gạt bỏ các gợi ý 1, 2, 3 và quyết định làm theo giải pháp số 4 (Workaround). Việc tải file .vsix trực tiếp từ trình duyệt web và import thủ công đã giúp tôi cài đặt thành công extension sơ đồ cơ sở dữ liệu một cách an toàn và dứt điểm, không cần thay đổi bất kỳ cài đặt hệ thống nào.</t>
+  </si>
+  <si>
+    <t>Decision-Making
+(System Architecture / Database Integration)</t>
+  </si>
+  <si>
+    <t>Prompt: "của tôi như vậy thì khác gì so với kiểu ntn, tôi có thể share database cho nhóm xài chung k"
+(Kèm ảnh cấu hình Local Database trên SSMS và ảnh Azure SQL Database của người khác).</t>
+  </si>
+  <si>
+    <t>Phản hồi: AI phân biệt rõ sự khác nhau giữa Local Database và Cloud Database. Đồng thời gợi ý dùng gói Azure for Students để tạo server chung hoặc dùng phần mềm Ngrok để mở port máy cá nhân.
+Kiểm chứng &amp; Quyết định: AI không biết rằng tài khoản Azure Student của tôi đang bị lỗi xác thực thẻ (Unable to complete verification). Hơn nữa, việc dùng Ngrok đòi hỏi tôi phải bật máy tính 24/24. Dựa trên tình hình thực tế, tôi đã tự đưa ra giải pháp mới: nhờ một bạn trong nhóm chưa từng dùng Azure dùng email của bạn đó tạo Server, sau đó tôi sẽ đảm nhận việc deploy Database từ máy Local của tôi lên Server đó. Quyết định này giúp nhóm có môi trường làm việc chung 24/7 cực kỳ ổn định mà không tốn chi phí hay phải treo máy liên tục.</t>
   </si>
   <si>
     <t>Decomposition / Abstraction</t>
@@ -153,30 +166,6 @@
 - Quyết định (Human Delta): Tôi nhận thấy thiết kế này thiếu tính mở rộng (Scalability), vì thực tế sinh viên có thể báo cáo cả Bình luận (comment) hoặc Tài khoản người dùng khác (user). Tôi đã áp dụng kỹ năng Trừu tượng hóa (Abstraction), thay post_id bằng hai cột target_type và target_id. Điều này giúp hệ thống báo cáo trở nên linh hoạt và dùng chung được cho mọi module.</t>
   </si>
   <si>
-    <t>Problem-Solving
-(Environment Setup / Tooling)</t>
-  </si>
-  <si>
-    <t>Prompt: "fĩx XHR failed"
-(Kèm ảnh chụp màn hình báo lỗi XHR failed trên tab Extension của Azure Data Studio).</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI phân tích nguyên nhân lỗi mạng và đề xuất 4 phương án: (1) Tắt Strict SSL, (2) Cấu hình Proxy, (3) Tắt IPv6/Đổi DNS, (4) Tải thủ công file .vsix để cài offline.
-Kiểm chứng &amp; Quyết định: Tôi nhận định việc can thiệp vào hệ thống mạng (tắt IPv6 hay đổi DNS) có thể gây lỗi mạng cho các phần mềm khác trên máy. Do đó, tôi chủ động gạt bỏ các gợi ý 1, 2, 3 và quyết định làm theo giải pháp số 4 (Workaround). Việc tải file .vsix trực tiếp từ trình duyệt web và import thủ công đã giúp tôi cài đặt thành công extension sơ đồ cơ sở dữ liệu một cách an toàn và dứt điểm, không cần thay đổi bất kỳ cài đặt hệ thống nào.</t>
-  </si>
-  <si>
-    <t>Decision-Making
-(System Architecture / Database Integration)</t>
-  </si>
-  <si>
-    <t>Prompt: "của tôi như vậy thì khác gì so với kiểu ntn, tôi có thể share database cho nhóm xài chung k"
-(Kèm ảnh cấu hình Local Database trên SSMS và ảnh Azure SQL Database của người khác).</t>
-  </si>
-  <si>
-    <t>Phản hồi: AI phân biệt rõ sự khác nhau giữa Local Database và Cloud Database. Đồng thời gợi ý dùng gói Azure for Students để tạo server chung hoặc dùng phần mềm Ngrok để mở port máy cá nhân.
-Kiểm chứng &amp; Quyết định: AI không biết rằng tài khoản Azure Student của tôi đang bị lỗi xác thực thẻ (Unable to complete verification). Hơn nữa, việc dùng Ngrok đòi hỏi tôi phải bật máy tính 24/24. Dựa trên tình hình thực tế, tôi đã tự đưa ra giải pháp mới: nhờ một bạn trong nhóm chưa từng dùng Azure dùng email của bạn đó tạo Server, sau đó tôi sẽ đảm nhận việc deploy Database từ máy Local của tôi lên Server đó. Quyết định này giúp nhóm có môi trường làm việc chung 24/7 cực kỳ ổn định mà không tốn chi phí hay phải treo máy liên tục.</t>
-  </si>
-  <si>
     <t>"Implement the Login page from Figma node 6-2, following 20 architecture rules (feature-based, Zustand, React Query, Zod…)"</t>
   </si>
   <si>
@@ -329,6 +318,234 @@
   <si>
     <t>- Phản hồi của AI: AI gợi ý kiểm tra xem hệ thống có chặn các file đuôi .exe hay .bat hay không.
 - Quyết định (Human Delta): Ý tưởng của AI quá cơ bản và dễ dàng bị bypass. Tôi áp dụng tư duy "Hacker" để mở rộng kịch bản: Thay vì chỉ kiểm tra đuôi file (Extension), tôi thiết kế case kiểm thử đổi đuôi file từ malware.exe thành malware.pdf nhưng bản chất bên trong vẫn là mã độc (kiểm tra MIME type/Magic Number). Tôi cũng thêm kịch bản nén file bom dung lượng (Zip Bomb) để test xem hệ thống có bị nghẽn RAM khi giải nén hay không, giúp tối ưu hóa tầng bảo mật cho ứng dụng.</t>
+  </si>
+  <si>
+    <t>"Scaffold backend SEHUB theo Clean Architecture: API, Application, Domain, Infrastructure, Contracts. Tách Auth, Posts, Exams thành module riêng."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI tạo cấu trúc solution với 6 project, đặt business logic trong Application Services, Entity trong Domain, DbContext trong Infrastructure.
+- Quyết định (Human Delta): Tôi chấp nhận khung Clean Architecture nhưng yêu cầu AI không đặt DTO trực tiếp trong Controller — mọi request/response phải qua Contracts. Đồng thời tôi tự bổ sung layer Shared cho constants và Result&lt;T&gt; pattern để chuẩn hóa API response cho Frontend.</t>
+  </si>
+  <si>
+    <t>"Implement JWT Authentication cho API SEHUB: login, refresh token, role-based authorization (Student/Moderator/Admin)."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI gợi ý lưu JWT trong HttpOnly Cookie và dùng session server-side thay vì stateless JWT.
+- Kiểm chứng &amp; Quyết định: Dự án FE đã dùng axios + Bearer token trong localStorage (từ tuần 3). Chuyển sang Cookie-based sẽ phá vỡ toàn bộ auth flow đã implement. Tôi đã bác bỏ gợi ý Cookie, giữ JWT stateless với accessToken (15 phút) + refreshToken (7 ngày) lưu trong bảng refresh_tokens, đồng bộ với Zustand authStore phía FE.</t>
+  </si>
+  <si>
+    <t>"Cấu hình EF Core Global Query Filter cho soft-delete (deleted_at) trên toàn bộ entity SEHUB."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI viết HasQueryFilter(e =&gt; e.DeletedAt == null) cho từng entity trong OnModelCreating.
+- Quyết định (Human Delta): Cách này đúng nhưng AI quên bỏ qua trường hợp Admin cần xem bản ghi đã xóa (Moderation History). Tôi đã tự thêm phương thức IgnoreQueryFilters() trong repository khi query audit, và viết extension ApplySoftDeleteFilter&lt;T&gt;() để tránh lặp code cho 40+ entity.</t>
+  </si>
+  <si>
+    <t>"Đăng ký DbContext là Scoped hay Singleton trong Program.cs?"</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI khuyên dùng AddDbContext với lifetime Singleton để tăng performance.
+- Kiểm chứng (Hallucination): Đây là lỗi nghiêm trọng — DbContext không thread-safe, Singleton sẽ gây race condition và memory leak khi có nhiều request đồng thời. Tôi đã sửa lại AddDbContext&lt;SEHubDbContext&gt;(options =&gt; ..., ServiceLifetime.Scoped) và thêm DbContextFactory cho background job nếu cần.</t>
+  </si>
+  <si>
+    <t>"Nên dùng Repository Pattern + Unit of Work hay gọi DbContext trực tiếp trong Service?"</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI tạo IGenericRepository&lt;T&gt; + IUnitOfWork bọc toàn bộ DbSet, mỗi entity một repository class.
+- Quyết định (Human Delta): Generic Repository chỉ là thin wrapper quanh DbContext, thêm layer không mang lại giá trị test. Tôi đã loại bỏ Generic Repository, chỉ giữ các repository đặc thù có query phức tạp (IPostRepository với FULLTEXT search, IExamRepository với Include questions). Service layer gọi DbContext trực tiếp cho CRUD đơn giản — đúng tinh thần pragmatism của Clean Architecture.</t>
+  </si>
+  <si>
+    <t>Decision-Making</t>
+  </si>
+  <si>
+    <t>"Tích hợp cổng thanh toán PayOS: webhook callback xác nhận đơn hàng Premium."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI viết endpoint webhook chỉ kiểm tra orderId khớp rồi cập nhật is_paid = true.
+- Kiểm chứng &amp; Quyết định: Thiếu xác thực chữ ký (checksum) từ PayOS — attacker có thể gửi request giả để kích hoạt Premium miễn phí. Tôi đã tự bổ sung HMAC-SHA256 signature validation theo docs PayOS, thêm idempotency check (không xử lý 2 lần cùng orderId), và ghi log vào token_audit_logs như đã thiết kế ở tuần 2.</t>
+  </si>
+  <si>
+    <t>"API GET /api/posts — nên dùng offset pagination hay cursor-based pagination?"</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI dùng Skip/Take với pageNumber và pageSize, kèm SELECT COUNT(*) để trả totalPages.
+- Quyết định (Human Delta): Offset pagination gây performance issue khi OFFSET lớn (feed có hàng nghìn bài). COUNT(*) trên bảng posts cũng chậm. Tôi đã chuyển sang cursor-based: client gửi lastPostId + lastCreatedAt, server query WHERE (created_at, id) &lt; (@cursor) ORDER BY created_at DESC LIMIT 20. Bỏ COUNT(*) — FE dùng hasMore flag thay totalPages.</t>
+  </si>
+  <si>
+    <t>"Có nên dùng MediatR (CQRS) cho toàn bộ API SEHUB không?"</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI strongly recommend MediatR + CQRS cho mọi endpoint, tạo CreatePostCommand, CreatePostHandler riêng.
+- Kiểm chứng &amp; Quyết định: AI over-engineered — team 4 người, deadline gấp, CRUD đơn giản không cần CQRS ceremony. MediatR thêm indirection khó debug cho junior dev. Tôi đã từ chối MediatR, giữ Service class trực tiếp (PostService.CreateAsync). Chỉ áp dụng Command pattern cho luồng phức tạp: SubmitExamAttempt (nhiều bước: validate → score → update points → notify).</t>
+  </si>
+  <si>
+    <t>"FE gọi API bị lỗi CORS: No Access-Control-Allow-Origin header."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI gợi ý thêm AllowAnyOrigin() trong CORS policy.
+- Kiểm chứng &amp; Quyết định: AllowAnyOrigin() không tương thích với AllowCredentials() — auth cookie/token sẽ fail. Tôi đã cấu hình WithOrigins("http://localhost:5173", "https://sehub.vercel.app").AllowCredentials().AllowAnyHeader().AllowAnyMethod(), đồng thời bật UseCors() trước UseAuthentication() trong pipeline.</t>
+  </si>
+  <si>
+    <t>"Viết Integration Test cho AuthController bằng WebApplicationFactory."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI tạo test dùng InMemory database provider thay vì SQL Server thật.
+- Quyết định (Human Delta): InMemory provider không hỗ trợ raw SQL, FULLTEXT, CHECK constraint — test pass nhưng production fail. Tôi đã chuyển sang Testcontainers (SQL Server container) cho integration test quan trọng (auth flow, soft-delete filter). Unit test vẫn dùng mock cho service layer.</t>
+  </si>
+  <si>
+    <t>"Implement phân hệ Feed bài viết (Figma node 12-xx): danh sách bài viết, tạo bài, like, comment — theo 20 architecture rules đã dùng ở Auth."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI tạo features/feed/ với api/, hooks/, components/, pages/ tương tự auth. Thêm useInfinitePosts hook dùng React Query useInfiniteQuery.
+- Quyết định (Human Delta): Chấp nhận cấu trúc feature-based. Tôi yêu cầu tách PostCard, PostActions, CommentThread vào shared/components/ vì Moderator và Profile cũng cần reuse — tránh duplicate UI giữa feed và featured posts.</t>
+  </si>
+  <si>
+    <t>"Infinite scroll cho feed: load thêm bài khi user scroll xuống cuối trang."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI dùng window scroll event listener + manual page state increment.
+- Kiểm chứng &amp; Quyết định: Cách này không tương thích với React Query cache invalidation và gây memory leak nếu không remove listener. Tôi đã chuyển sang useInfiniteQuery với getNextPageParam đọc cursor từ API (lastPostId), kết hợp IntersectionObserver trên sentinel div — pattern chuẩn, tự động merge pages vào cache.</t>
+  </si>
+  <si>
+    <t>"Editor Markdown cho tạo bài viết — cần sanitize HTML để chống XSS."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI gợi ý dùng dangerouslySetInnerHTML trực tiếp với output từ marked.js.
+- Kiểm chứng (Hallucination): Đây là lỗ hổng XSS nghiêm trọng — attacker có thể inject &lt;script&gt; trong Markdown. Tôi đã thay bằng DOMPurify.sanitize() sau khi render Markdown, whitelist chỉ các tag an toàn (p, h1-h6, strong, em, a, img, code, pre). Backend cũng validate content_md length ≤ 10.000 ký tự theo CHECK constraint tuần 2.</t>
+  </si>
+  <si>
+    <t>"Figma MCP quota hết — implement màn Exam List và Exam Detail từ node 18-xx, 19-xx."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI không đọc được Figma node, đoán layout dựa trên pattern Feed (card list + detail page).
+- Quyết định (Human Delta): Chấp nhận implement theo pattern hiện có (card grid, sidebar filter theo subject). Đánh dấu cần pixel-perfect review khi MCP quota reset. npm run build passed; flow /exams → /exams/:id → start attempt hoạt động với mock API.</t>
+  </si>
+  <si>
+    <t>"Thiết kế component ExamQuestion cho cả chế độ làm bài (student) và chế độ preview (moderator)."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI tạo 2 component riêng: ExamQuestionStudent và ExamQuestionPreview với 80% code trùng lặp.
+- Quyết định (Human Delta): Vi phạm DRY. Tôi đã refactor thành 1 component ExamQuestion với props mode: 'attempt' | 'preview' | 'review', showAnswer: boolean, onSelectAnswer callback. Moderator preview dùng mode='preview'; student làm bài dùng mode='attempt' với timer countdown.</t>
+  </si>
+  <si>
+    <t>"Realtime notification khi có comment mới — dùng WebSocket (SignalR) hay polling?"</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI recommend SignalR Hub cho mọi realtime event (comment, like, chat, notification).
+- Kiểm chứng &amp; Quyết định: SignalR cần BE deploy sticky session + Redis backplane — phức tạp cho Giai đoạn 1. Comment notification không cần realtime tức thì. Tôi đã chọn React Query refetchInterval: 30s cho notification badge, reserve SignalR cho chat 1-1 (tuần 7). Tránh over-engineering infrastructure.</t>
+  </si>
+  <si>
+    <t>"Upload ảnh đính kèm bài viết — flow upload trực tiếp lên server hay qua presigned URL?"</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI viết endpoint nhận multipart/form-data, lưu file vào wwwroot/uploads/ trên server.
+- Quyết định (Human Delta): Lưu local không scale, mất ảnh khi redeploy container. Tôi đã chuyển sang flow: FE gọi POST /api/posts/upload-url → BE trả presigned URL (Cloudinary) → FE upload trực tiếp lên CDN → gửi imageUrl khi tạo post. Giảm tải BE, ảnh persist qua deploy.</t>
+  </si>
+  <si>
+    <t>Pattern Recognition / Decision-Making</t>
+  </si>
+  <si>
+    <t>"Vẽ lại Screen Flow Figure 4 (Moderator) theo tài liệu BA — AI diagram cũ có Assign Badges và Delete Course."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI xác nhận diagram cũ sai: Moderator không được Assign Badges (thuộc Admin), không Delete Course (chỉ tạo đề chờ duyệt).
+- Quyết định (Human Delta): Tôi đã tách Report Queue thành 2 luồng: Content Report (xóa/giữ + lý do) và User Report (cảnh báo, khóa 1/7/30 ngày). Thêm luồng chấm bài thực hành (GitHub URL → Đạt/Chưa đạt). Xuất file SVG SEHUB_Figure4_Moderator_Screen_Flow.svg làm tài liệu chuẩn cho team FE.</t>
+  </si>
+  <si>
+    <t>"Merge main vào nhánh Hau_BE — conflict HeaderUserActions và ProfileMenu (Redux vs Zustand)."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI gợi ý giữ cả Redux và Zustand song song, dispatch cả hai khi logout.
+- Kiểm chứng &amp; Quyết định: Dual state management gây desync session. Tôi giữ phiên bản Zustand (clearAuthSession + navigate), loại bỏ Redux dispatch trong HeaderUserActions. Kiểm tra toàn bộ component còn import useSelector — migrate dần, không revert về Redux.</t>
+  </si>
+  <si>
+    <t>"Test luồng Moderator: duyệt báo cáo → pin bài viết → tạo đề thi draft → submit Admin."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI viết test manual checklist 15 bước.
+- Quyết định (Human Delta): Tôi đã chạy thử trên dev server port 5180, phát hiện bug: sau khi pin bài viết, Featured Posts page không refetch (stale cache). Fix bằng queryClient.invalidateQueries(['featured-posts']) trong onSuccess mutation. Ghi nhận vào bug log, severity Medium.</t>
+  </si>
+  <si>
+    <t>Decomposition / Decision-Making</t>
+  </si>
+  <si>
+    <t>"Migrate database từ Azure SQL sang Supabase PostgreSQL — cần thay đổi gì trong EF Core?"</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI gợi ý chỉ đổi connection string, EF Core tự handle dialect khác.
+- Kiểm chứng &amp; Quyết định: AI oversimplified — SQL Server dùng NVARCHAR, UNIQUEIDENTIFIER, DATETIME2; PostgreSQL dùng TEXT, UUID, TIMESTAMPTZ. FULLTEXT INDEX syntax hoàn toàn khác (tsvector vs CONTAINS). Tôi đã: (1) đổi provider sang Npgsql, (2) viết migration script chuyển đổi kiểu dữ liệu, (3) thay FULLTEXT bằng GIN index trên to_tsvector('vietnamese', content_text), (4) test lại toàn bộ query trước khi merge.</t>
+  </si>
+  <si>
+    <t>"API GET /api/feed chậm 3-5 giây khi có 500+ bài viết — profiling và tối ưu."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI gợi ý thêm Redis cache cho toàn bộ response feed.
+- Quyết định (Human Delta): Cache full response gây stale data khi có bài mới/like mới. Tôi dùng dotnet-ctrace + SQL Profiler, phát hiện N+1 query: load posts rồi loop Include Author, Likes, Comments cho từng post. Fix: dùng .Include().ThenInclude() + .AsSplitQuery(), projection sang DTO thay vì load full entity. Response time giảm từ 3.2s xuống 280ms.</t>
+  </si>
+  <si>
+    <t>"Refactor AI Explanation Service — AI gợi ý gửi full exam content kèm đáp án cho OpenAI API."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI viết prompt gửi toàn bộ đề thi + đáp án đúng cho GPT-4 để giải thích.
+- Kiểm chứng (Hallucination): Rủi ro lộ đáp án qua prompt injection; tốn token không cần thiết. Tôi đã refactor: chỉ gửi 1 câu hỏi + đáp án đã chọn + đáp án đúng (plain text, không markdown), enforce giới hạn tokens_used per message (đã thiết kế tuần 2). Đổi tên service thành AiExplanationService, validate input length trước khi gọi API.</t>
+  </si>
+  <si>
+    <t>"Improve feed, auth, and admin performance across Phases 1-3 — AI đề xuất danh sách tối ưu."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI liệt kê 20 mục tối ưu: lazy loading, code splitting, memo, virtual list, service worker, CDN, database indexing...
+- Quyết định (Human Delta): Tôi ưu tiên theo impact/effort: Phase 1 (N+1 fix, React.memo PostCard, pagination cursor), Phase 2 (lazy route import, image lazy load), Phase 3 (virtual scroll feed — defer vì cần thư viện thêm). Không implement service worker (out of scope Giai đoạn 1). Đo lường bằng Lighthouse trước/sau: Performance score 62 → 81.</t>
+  </si>
+  <si>
+    <t>"SignalR Chat Hub — connection bị disconnect sau 30 giây không hoạt động."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI gợi ý tăng server timeout lên 5 phút trong appsettings.json.
+- Kiểm chứng &amp; Quyết định: Tăng timeout chỉ trì hoãn vấn đề, không fix root cause. Thực tế do Azure App Service idle timeout và thiếu keep-alive. Tôi đã implement: (1) client-side hub.onclose() → auto reconnect với exponential backoff, (2) server ping mỗi 15s qua hub.SendAsync('ping'), (3) client trả 'pong'. Connection ổn định qua 2 giờ test.</t>
+  </si>
+  <si>
+    <t>"Quản lý secrets (API key OpenAI, PayOS, Cloudinary) — lưu ở đâu an toàn?"</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI gợi ý hardcode trong appsettings.Development.json và commit vào git.
+- Kiểm chứng (Hallucination): Vi phạm bảo mật nghiêm trọng — API key lộ trên GitHub. Tôi đã: (1) dùng dotnet user-secrets cho local dev, (2) tạo LOCAL_SECRETS.template.md (không commit giá trị thật), (3) Azure App Service Configuration / Supabase env vars cho production, (4) thêm .gitignore cho appsettings.*.local.json. Xóa file secrets đã lỡ commit khỏi git history.</t>
+  </si>
+  <si>
+    <t>Algorithmic Thinking / Verification</t>
+  </si>
+  <si>
+    <t>"Implement Question Reporting Feature — sinh viên báo cáo câu hỏi đề thi sai đáp án."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI tạo bảng question_reports với cột question_id và reason text.
+- Quyết định (Human Delta): Tôi reuse bảng reports đã thiết kế tuần 2 (target_type + target_id) thay vì tạo bảng mới — tránh schema sprawl. Thêm target_type='question' vào enum. Workflow: Student report → Moderator review queue → forward Admin nếu cần sửa đề. Viết unit test cho ModerationService.ReportQuestionAsync() với mock IWorkflowNotificationService.</t>
+  </si>
+  <si>
+    <t>Evaluation / Decision-Making</t>
+  </si>
+  <si>
+    <t>"Chuẩn bị demo cuối kỳ — AI liệt kê 8 bug High severity cần fix trước khi present."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI classify: UI lệch 2px mobile, font size khác Figma 1px, màu button hover sai, thiếu loading skeleton...
+- Quyết định (Human Delta): Tôi bác bỏ 5/8 bug cosmetic (giống đánh giá tuần 4). Ưu tiên 3 bug thực sự block demo: (1) Premium payment callback không cập nhật is_premium, (2) Exam timer không pause khi switch tab, (3) Chat message duplicate khi reconnect SignalR. Fix xong 3 bug này trước deadline; cosmetic để backlog sprint sau.</t>
+  </si>
+  <si>
+    <t>"Chạy full E2E test trước demo: Register → Login → Tạo bài → Làm đề → Nạp Premium → Chat AI."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI viết script Selenium chạy tuần tự 45 phút với Thread.Sleep giữa các bước.
+- Kiểm chứng &amp; Quyết định: Áp dụng bài học tuần 4 — loại bỏ Thread.Sleep, dùng Explicit Wait. Tuy nhiên, 45 phút quá lâu cho CI. Tôi tách thành 3 suite độc lập (Auth 5 phút, Feed+Exam 10 phút, Payment+Chatbot 8 phút) chạy parallel trên GitHub Actions. Kết quả: 2 suite pass, 1 fail do PayOS sandbox timeout — chấp nhận demo bằng mock payment.</t>
+  </si>
+  <si>
+    <t>Abstraction / Decomposition</t>
+  </si>
+  <si>
+    <t>"Tổng kết dự án SEHUB Giai đoạn 1 — viết README và hướng dẫn deploy cho team."</t>
+  </si>
+  <si>
+    <t>- Phản hồi của AI: AI sinh README generic với npm install &amp;&amp; npm start, không đề cập BE .NET hay database migration.
+- Quyết định (Human Delta): README của AI thiếu context dự án thực tế. Tôi đã tự viết lại: (1) Prerequisites (.NET 8, Node 20, Supabase account), (2) BE setup (dotnet ef database update, user-secrets), (3) FE setup (VITE_API_URL), (4) Docker compose cho local full-stack, (5) Known issues &amp; Giai đoạn 2 roadmap (pre-moderation, OCR đề thi). Giao cho team onboard trong 30 phút thay vì 3 giờ.</t>
   </si>
 </sst>
 </file>
@@ -364,12 +581,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -379,8 +590,13 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -408,12 +624,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor rgb="FF1F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
         <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
@@ -475,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -486,10 +696,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -505,17 +715,23 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -850,102 +1066,102 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59E3EFE9-6FFB-49CC-BE69-0C0E36C6253E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" customWidth="1"/>
-    <col min="2" max="2" width="31.88671875" customWidth="1"/>
-    <col min="3" max="3" width="33.109375" customWidth="1"/>
-    <col min="4" max="4" width="59.109375" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" customWidth="1"/>
+    <col min="2" max="2" width="31.85546875" customWidth="1"/>
+    <col min="3" max="3" width="33.140625" customWidth="1"/>
+    <col min="4" max="4" width="59.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="5" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:5" ht="206.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="206.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6">
         <v>1</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>34</v>
+        <v>5</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="267" customHeight="1" x14ac:dyDescent="0.3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="267" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8">
         <v>2</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
       <c r="D9" s="2"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
@@ -957,169 +1173,169 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EFBDDC7E-59F2-4CBB-B3D2-F6FB78F9E873}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="26.88671875" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" customWidth="1"/>
-    <col min="4" max="4" width="76.33203125" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" customWidth="1"/>
+    <col min="4" max="4" width="76.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="5" customFormat="1" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" ht="72" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="72" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" ht="100.8" x14ac:dyDescent="0.3">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="100.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -1128,37 +1344,37 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{323516A4-AE23-41CF-AD84-97A6064FC5FB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21" customWidth="1"/>
-    <col min="2" max="2" width="26.88671875" customWidth="1"/>
-    <col min="3" max="3" width="24.33203125" customWidth="1"/>
-    <col min="4" max="4" width="76.33203125" customWidth="1"/>
+    <col min="2" max="2" width="26.85546875" customWidth="1"/>
+    <col min="3" max="3" width="24.28515625" customWidth="1"/>
+    <col min="4" max="4" width="76.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="5" customFormat="1" ht="31.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="5" customFormat="1" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>2</v>
-      </c>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" spans="1:5" ht="86.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" ht="86.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>39</v>
@@ -1167,7 +1383,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1181,7 +1397,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1195,12 +1411,12 @@
         <v>46</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>47</v>
@@ -1209,12 +1425,12 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>49</v>
@@ -1223,12 +1439,12 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>51</v>
@@ -1237,12 +1453,12 @@
         <v>52</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>53</v>
@@ -1251,7 +1467,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1265,12 +1481,12 @@
         <v>57</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>58</v>
@@ -1279,12 +1495,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>60</v>
@@ -1299,170 +1515,680 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{540CDA82-72CC-4977-B394-F64FA908FB7E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="48.109375" customWidth="1"/>
+    <col min="2" max="2" width="48.140625" customWidth="1"/>
     <col min="3" max="3" width="39" customWidth="1"/>
-    <col min="4" max="4" width="85.5546875" customWidth="1"/>
+    <col min="4" max="4" width="85.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:4" ht="40.9" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="11" t="s">
+    </row>
+    <row r="2" spans="1:4" ht="167.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="11">
         <v>1</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="B2" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D2" s="13" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" ht="167.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="12">
-        <v>1</v>
-      </c>
-      <c r="B2" s="13" t="s">
+      <c r="B3" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="11">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="11">
         <v>4</v>
       </c>
-      <c r="C2" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="12">
-        <v>2</v>
-      </c>
-      <c r="B3" s="13" t="s">
+      <c r="B5" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D5" s="13" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="11">
+        <v>5</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="D6" s="13" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="11">
+        <v>6</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C7" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="11">
+        <v>7</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="13" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="11">
+        <v>8</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="C9" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="11">
+        <v>9</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="409.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="11">
         <v>10</v>
       </c>
-      <c r="C3" s="14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="12">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>66</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="12">
-        <v>4</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="12">
-        <v>5</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="12">
-        <v>6</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="12">
-        <v>7</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>75</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="12">
-        <v>8</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>78</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="12">
-        <v>9</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>81</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="409.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="12">
-        <v>10</v>
-      </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C11" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="13" t="s">
         <v>85</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="4" max="4" width="75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A3" s="15">
+        <v>2</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
+        <v>6</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
+        <v>7</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
+        <v>8</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
+        <v>10</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="4" max="4" width="75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A3" s="15">
+        <v>2</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
+        <v>6</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
+        <v>7</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
+        <v>8</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="75" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
+        <v>10</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>127</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
+    <col min="3" max="3" width="55" customWidth="1"/>
+    <col min="4" max="4" width="75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="120" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
+        <v>1</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>129</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A3" s="15">
+        <v>2</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
+        <v>3</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>133</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>135</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
+        <v>5</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>77</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>137</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
+        <v>6</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="90" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
+        <v>7</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>142</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
+        <v>8</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>144</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>145</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>147</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="105" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
+        <v>10</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>150</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>151</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>